--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_jk_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_jk_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>19-06-2021 08:30</t>
+          <t>2021-06-19 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10-07-2021 08:30</t>
+          <t>2021-10-07 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>19-06-2021 08:30</t>
+          <t>2021-06-19 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>10-07-2021 08:30</t>
+          <t>2021-10-07 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>19-06-2021 08:30</t>
+          <t>2021-06-19 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>10-07-2021 08:30</t>
+          <t>2021-10-07 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>19-06-2021 08:30</t>
+          <t>2021-06-19 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>10-07-2021 08:30</t>
+          <t>2021-10-07 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>19-06-2021 08:30</t>
+          <t>2021-06-19 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>10-07-2021 08:30</t>
+          <t>2021-10-07 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="n">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>19-05-2021 08:30</t>
+          <t>2021-05-19 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="n">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>27-09-2021 08:30</t>
+          <t>2021-09-27 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="n">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="n">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="n">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="n">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="n">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="n">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="n">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="n">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="n">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="n">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="n">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="n">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>27-09-2021 08:30</t>
+          <t>2021-09-27 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="n">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="n">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="n">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -14203,7 +14203,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="inlineStr"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="inlineStr"/>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="inlineStr"/>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="n">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="n">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="n">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="n">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="n">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="n">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16204,7 +16204,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="inlineStr"/>
@@ -16582,7 +16582,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16677,7 +16677,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="n">
@@ -17057,7 +17057,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -17152,7 +17152,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="n">
@@ -17247,7 +17247,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="n">
@@ -17342,7 +17342,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="n">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>12-11-2021 08:30</t>
+          <t>2021-12-11 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="n">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="n">
@@ -17722,7 +17722,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="inlineStr"/>
@@ -17815,7 +17815,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="inlineStr"/>
@@ -17908,7 +17908,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="inlineStr"/>
@@ -18001,7 +18001,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="inlineStr"/>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="inlineStr"/>
@@ -18187,7 +18187,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="inlineStr"/>
@@ -18280,7 +18280,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="inlineStr"/>
@@ -18373,7 +18373,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="inlineStr"/>
@@ -18466,7 +18466,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="inlineStr"/>
@@ -18559,7 +18559,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>16-10-2021 08:30</t>
+          <t>2021-10-16 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="n">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="n">
@@ -18755,7 +18755,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="n">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="n">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="n">
@@ -19040,7 +19040,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="inlineStr"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="inlineStr"/>
@@ -19226,7 +19226,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="inlineStr"/>
@@ -19319,7 +19319,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="inlineStr"/>
@@ -19412,7 +19412,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="inlineStr"/>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="inlineStr"/>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="inlineStr"/>
@@ -19691,7 +19691,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="inlineStr"/>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="inlineStr"/>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="inlineStr"/>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="inlineStr"/>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="inlineStr"/>
@@ -20156,7 +20156,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="inlineStr"/>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="inlineStr"/>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -20435,7 +20435,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="inlineStr"/>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="inlineStr"/>
@@ -20714,7 +20714,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="inlineStr"/>
@@ -20807,7 +20807,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="inlineStr"/>
@@ -20900,7 +20900,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="inlineStr"/>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="inlineStr"/>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="inlineStr"/>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="inlineStr"/>
@@ -21272,7 +21272,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="n">
@@ -21373,7 +21373,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="inlineStr"/>
@@ -21466,7 +21466,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="n">
@@ -21656,7 +21656,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="n">
@@ -21751,7 +21751,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="n">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="n">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="n">
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>28-05-2021 08:30</t>
+          <t>2021-05-28 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="n">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="n">
@@ -22416,7 +22416,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="n">
@@ -22511,7 +22511,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="n">
@@ -22606,7 +22606,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="n">
@@ -22701,7 +22701,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="n">
@@ -22796,7 +22796,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="n">
@@ -22891,7 +22891,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="n">
@@ -22986,7 +22986,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="n">
@@ -23081,7 +23081,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="n">
@@ -23176,7 +23176,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="n">
@@ -23271,7 +23271,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="n">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="n">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="n">
@@ -23556,7 +23556,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="n">
@@ -23651,7 +23651,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="n">
@@ -23746,7 +23746,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="n">
@@ -23841,7 +23841,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="n">
@@ -23936,7 +23936,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="n">
@@ -24031,7 +24031,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="n">
@@ -24126,7 +24126,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="n">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="n">
@@ -24316,7 +24316,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="n">
@@ -24411,7 +24411,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="n">
@@ -24506,7 +24506,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="n">
@@ -24601,7 +24601,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="n">
@@ -24696,7 +24696,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="n">
@@ -24791,7 +24791,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="n">
